--- a/csv/policies/reference/Ref_coal phase out/formula_Ref_coal phase out_AT.xlsx
+++ b/csv/policies/reference/Ref_coal phase out/formula_Ref_coal phase out_AT.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="40545" yWindow="3660" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -587,7 +587,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
